--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" tabRatio="713" firstSheet="6" activeTab="9"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" tabRatio="713"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t>size</t>
   </si>
@@ -92,11 +92,38 @@
   <si>
     <t>ValveList</t>
   </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>12.0</t>
+  </si>
+  <si>
+    <t>16.0</t>
+  </si>
+  <si>
+    <t>20.0</t>
+  </si>
+  <si>
+    <t>30.0</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -260,7 +287,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -274,19 +301,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -329,6 +344,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -858,8 +891,8 @@
       <c r="G1" s="4"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2</v>
+      <c r="A2" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B2" s="2">
         <v>600</v>
@@ -878,8 +911,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>1</v>
+      <c r="A3" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="B3" s="2">
         <v>600</v>
@@ -898,8 +931,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>4</v>
+      <c r="A4" s="2" t="s">
+        <v>22</v>
       </c>
       <c r="B4" s="2">
         <v>600</v>
@@ -918,8 +951,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>8</v>
+      <c r="A5" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B5" s="2">
         <v>600</v>
@@ -938,8 +971,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>12</v>
+      <c r="A6" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="B6" s="2">
         <v>600</v>
@@ -958,8 +991,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>16</v>
+      <c r="A7" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="B7" s="2">
         <v>600</v>
@@ -978,8 +1011,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>20</v>
+      <c r="A8" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="B8" s="2">
         <v>600</v>
@@ -998,8 +1031,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>30</v>
+      <c r="A9" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B9" s="2">
         <v>600</v>
@@ -1018,8 +1051,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>8</v>
+      <c r="A10" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="B10" s="2">
         <v>600</v>
@@ -1062,230 +1095,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="23">
         <f>'[1]8E43'!A2</f>
         <v>0</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="24">
         <f>'[1]8E43'!B2</f>
         <v>0</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="21">
         <f>'[1]8E43'!C2</f>
         <v>0</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="21">
         <f>'[1]8E43'!D2</f>
         <v>0</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+      <c r="A3" s="23">
         <f>'[1]8E43'!A3</f>
         <v>10</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="24">
         <f>'[1]8E43'!B3</f>
         <v>0</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="21">
         <f>'[1]8E43'!C3</f>
         <v>0</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="21">
         <f>'[1]8E43'!D3</f>
         <v>0</v>
       </c>
-      <c r="E3" s="7"/>
+      <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="23">
         <f>'[1]8E43'!A4</f>
         <v>25</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="24">
         <f>'[1]8E43'!B4</f>
         <v>18.986232644492688</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="21">
         <f>'[1]8E43'!C4</f>
         <v>0.36</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="21">
         <f>'[1]8E43'!D4</f>
         <v>0.6</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="A5" s="23">
         <f>'[1]8E43'!A5</f>
         <v>30</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="24">
         <f>'[1]8E43'!B5</f>
         <v>44.383454121572619</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="21">
         <f>'[1]8E43'!C5</f>
         <v>0.38651089000000005</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="21">
         <f>'[1]8E43'!D5</f>
         <v>0.62170000000000003</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="23">
         <f>'[1]8E43'!A6</f>
         <v>40</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="24">
         <f>'[1]8E43'!B6</f>
         <v>142.05858314674643</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="21">
         <f>'[1]8E43'!C6</f>
         <v>0.38254225000000008</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="21">
         <f>'[1]8E43'!D6</f>
         <v>0.61850000000000005</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="A7" s="23">
         <f>'[1]8E43'!A7</f>
         <v>50</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="24">
         <f>'[1]8E43'!B7</f>
         <v>260.93930660910786</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="21">
         <f>'[1]8E43'!C7</f>
         <v>0.35164899999999999</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="21">
         <f>'[1]8E43'!D7</f>
         <v>0.59299999999999997</v>
       </c>
-      <c r="E7" s="7"/>
+      <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="23">
         <f>'[1]8E43'!A8</f>
         <v>60</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="24">
         <f>'[1]8E43'!B8</f>
         <v>457.75779764190349</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="21">
         <f>'[1]8E43'!C8</f>
         <v>0.33524099999999996</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="21">
         <f>'[1]8E43'!D8</f>
         <v>0.57899999999999996</v>
       </c>
-      <c r="E8" s="7"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="A9" s="23">
         <f>'[1]8E43'!A9</f>
         <v>70</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="24">
         <f>'[1]8E43'!B9</f>
         <v>777.14975431228527</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="21">
         <f>'[1]8E43'!C9</f>
         <v>0.26936100000000002</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="21">
         <f>'[1]8E43'!D9</f>
         <v>0.51900000000000002</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="23">
         <f>'[1]8E43'!A10</f>
         <v>80</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="24">
         <f>'[1]8E43'!B10</f>
         <v>984.39348661726467</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="21">
         <f>'[1]8E43'!C10</f>
         <v>0.28462224999999997</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="21">
         <f>'[1]8E43'!D10</f>
         <v>0.53349999999999997</v>
       </c>
-      <c r="E10" s="7"/>
+      <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="A11" s="23">
         <f>'[1]8E43'!A11</f>
         <v>90</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="24">
         <f>'[1]8E43'!B11</f>
         <v>1115.0442453350299</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="21">
         <f>'[1]8E43'!C11</f>
         <v>0.33639999999999998</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="21">
         <f>'[1]8E43'!D11</f>
         <v>0.57999999999999996</v>
       </c>
-      <c r="E11" s="7"/>
+      <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="25">
         <f>'[1]8E43'!A12</f>
         <v>100</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="26">
         <f>'[1]8E43'!B12</f>
         <v>1145.7583178945802</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="22">
         <f>'[1]8E43'!C12</f>
         <v>0.37209999999999999</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="22">
         <f>'[1]8E43'!D12</f>
         <v>0.61</v>
       </c>
-      <c r="E12" s="10"/>
+      <c r="E12" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1304,186 +1337,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23"/>
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>3.28</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>7.39</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.60499999999999998</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.61699999999999999</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>14.2</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>14.9</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>15.3</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.79</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>15.7</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>16.399999999999999</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>16.8</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1503,186 +1536,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0</v>
-      </c>
-      <c r="E2" s="16"/>
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0</v>
+      </c>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>5</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="11">
         <v>0.55000000000000004</v>
       </c>
-      <c r="D3" s="15">
+      <c r="D3" s="11">
         <v>0.3</v>
       </c>
-      <c r="E3" s="16"/>
+      <c r="E3" s="12"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>15</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="11">
         <v>0.6</v>
       </c>
-      <c r="D4" s="15">
+      <c r="D4" s="11">
         <v>0.4</v>
       </c>
-      <c r="E4" s="16"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>30</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="11">
         <v>0.65</v>
       </c>
-      <c r="D5" s="15">
+      <c r="D5" s="11">
         <v>0.5</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="12"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>45</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="11">
         <v>0.7</v>
       </c>
-      <c r="D6" s="15">
+      <c r="D6" s="11">
         <v>0.6</v>
       </c>
-      <c r="E6" s="16"/>
+      <c r="E6" s="12"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>60</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="11">
         <v>0.75</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="11">
         <v>0.65</v>
       </c>
-      <c r="E7" s="16"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>75</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="11">
         <v>0.8</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="11">
         <v>0.7</v>
       </c>
-      <c r="E8" s="16"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>85</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="11">
         <v>0.82</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="11">
         <v>0.75</v>
       </c>
-      <c r="E9" s="16"/>
+      <c r="E9" s="12"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>92</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="11">
         <v>0.83</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="11">
         <v>0.78</v>
       </c>
-      <c r="E10" s="16"/>
+      <c r="E10" s="12"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>98</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="11">
         <v>0.84</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="11">
         <v>0.8</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>100</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="14">
         <v>0.85</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="14">
         <v>0.81</v>
       </c>
-      <c r="E12" s="19"/>
+      <c r="E12" s="15"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1701,186 +1734,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23"/>
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>226</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.49</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>337</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.47</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>436</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.42699999999999999</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>502</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.45200000000000001</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>581</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.46800000000000003</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>641</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.51200000000000001</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>655</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.624</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>659</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.70299999999999996</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>659</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.70299999999999996</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>681</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14">
         <v>0.70099999999999996</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1899,186 +1932,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0</v>
-      </c>
-      <c r="E2" s="23"/>
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0</v>
+      </c>
+      <c r="D2" s="11">
+        <v>0</v>
+      </c>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>3.28</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>7.39</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.60499999999999998</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.61699999999999999</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>14.2</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>14.9</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>15.3</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.79</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>15.7</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>16.399999999999999</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>16.8</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2097,184 +2130,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="23"/>
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>3.28</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>7.39</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.60499999999999998</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.61699999999999999</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>14.2</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>14.9</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>15.3</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.79</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>15.7</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>16.399999999999999</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>16.8</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18">
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E12" s="24"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2293,184 +2326,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D2" s="11">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>3.28</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.60499999999999998</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>7.39</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.61699999999999999</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>14.2</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>14.9</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.79</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>15.3</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>15.7</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>16.399999999999999</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>16.8</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="24"/>
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2489,184 +2522,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D2" s="11">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>3.28</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.60499999999999998</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>7.39</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.61699999999999999</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>14.2</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>14.9</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.79</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>15.3</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>15.7</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>16.399999999999999</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>16.8</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="24"/>
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2685,184 +2718,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="14">
-        <v>0</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="15">
+      <c r="A2" s="10">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D2" s="11">
         <v>0.58099999999999996</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="19"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="14">
+      <c r="A3" s="10">
         <v>10</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="11">
         <v>3.28</v>
       </c>
-      <c r="C3" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="15">
+      <c r="C3" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="11">
         <v>0.60499999999999998</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="19"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="14">
+      <c r="A4" s="10">
         <v>20</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="11">
         <v>7.39</v>
       </c>
-      <c r="C4" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="15">
+      <c r="C4" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="11">
         <v>0.61699999999999999</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="14">
+      <c r="A5" s="10">
         <v>30</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="11">
         <v>12</v>
       </c>
-      <c r="C5" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="C5" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="11">
         <v>0.64400000000000002</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="19"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="14">
+      <c r="A6" s="10">
         <v>40</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="11">
         <v>14.2</v>
       </c>
-      <c r="C6" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="11">
         <v>0.76400000000000001</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="14">
+      <c r="A7" s="10">
         <v>50</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="11">
         <v>14.9</v>
       </c>
-      <c r="C7" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="11">
         <v>0.79</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="14">
+      <c r="A8" s="10">
         <v>60</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>15.3</v>
       </c>
-      <c r="C8" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="11">
         <v>0.80900000000000005</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="19"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="14">
+      <c r="A9" s="10">
         <v>70</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="11">
         <v>15.7</v>
       </c>
-      <c r="C9" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="11">
         <v>0.81299999999999994</v>
       </c>
-      <c r="E9" s="23"/>
+      <c r="E9" s="19"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="14">
+      <c r="A10" s="10">
         <v>80</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="11">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="15">
+      <c r="C10" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="11">
         <v>0.79500000000000004</v>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="19"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="14">
+      <c r="A11" s="10">
         <v>90</v>
       </c>
-      <c r="B11" s="15">
+      <c r="B11" s="11">
         <v>16.399999999999999</v>
       </c>
-      <c r="C11" s="15">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="11">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="11">
         <v>0.76800000000000002</v>
       </c>
-      <c r="E11" s="23"/>
+      <c r="E11" s="19"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="A12" s="13">
         <v>100</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="14">
         <v>16.8</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="24"/>
+      <c r="C12" s="14">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\2M\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\9V\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="9" activeTab="10"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="7" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="28">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E2" s="26"/>
     </row>
@@ -1181,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="28">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E3" s="26"/>
     </row>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="16">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E2" s="17"/>
     </row>
@@ -1761,7 +1761,8 @@
         <v>0</v>
       </c>
       <c r="D2" s="7">
-        <v>0</v>
+        <f>D3</f>
+        <v>0.58099999999999996</v>
       </c>
       <c r="E2" s="8"/>
     </row>
@@ -1959,7 +1960,8 @@
         <v>0</v>
       </c>
       <c r="D2" s="16">
-        <v>0</v>
+        <f>D3</f>
+        <v>0.58099999999999996</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2157,7 +2159,8 @@
         <v>0</v>
       </c>
       <c r="D2" s="16">
-        <v>0</v>
+        <f>D3</f>
+        <v>0.49</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2355,7 +2358,8 @@
         <v>0</v>
       </c>
       <c r="D2" s="16">
-        <v>0</v>
+        <f>D3</f>
+        <v>0.58099999999999996</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2552,7 +2556,10 @@
       <c r="C2" s="16">
         <v>0.68</v>
       </c>
-      <c r="D2" s="16"/>
+      <c r="D2" s="16">
+        <f>D3</f>
+        <v>0.58099999999999996</v>
+      </c>
       <c r="E2" s="24"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\9V\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\BG\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="7" activeTab="10"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="8" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -24,13 +24,14 @@
     <sheet name="Valve_30.0_600_3" sheetId="10" r:id="rId10"/>
     <sheet name="Valve_8.0_600_4" sheetId="11" r:id="rId11"/>
     <sheet name="Valve_2.0_1500_3" sheetId="12" r:id="rId12"/>
+    <sheet name="Valve_8.0_V250_5" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="23">
   <si>
     <t>size</t>
   </si>
@@ -96,6 +97,9 @@
   </si>
   <si>
     <t>ValveList</t>
+  </si>
+  <si>
+    <t>V250</t>
   </si>
 </sst>
 </file>
@@ -668,7 +672,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="9.140625" style="2"/>
@@ -914,6 +918,23 @@
       </c>
       <c r="F12" s="3" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>8</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2">
+        <v>5</v>
+      </c>
+      <c r="D13" s="2">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1526,6 +1547,209 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>0</v>
+      </c>
+      <c r="B2" s="16">
+        <v>0</v>
+      </c>
+      <c r="C2" s="16">
+        <v>0</v>
+      </c>
+      <c r="D2" s="16">
+        <v>0.4</v>
+      </c>
+      <c r="E2" s="24"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>10</v>
+      </c>
+      <c r="B3" s="16">
+        <v>50</v>
+      </c>
+      <c r="C3" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E3" s="24"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>20</v>
+      </c>
+      <c r="B4" s="16">
+        <v>100</v>
+      </c>
+      <c r="C4" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="16">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E4" s="24"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>30</v>
+      </c>
+      <c r="B5" s="16">
+        <v>150</v>
+      </c>
+      <c r="C5" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="E5" s="24"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>40</v>
+      </c>
+      <c r="B6" s="16">
+        <v>250</v>
+      </c>
+      <c r="C6" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="16">
+        <v>0.65</v>
+      </c>
+      <c r="E6" s="24"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>50</v>
+      </c>
+      <c r="B7" s="16">
+        <v>400</v>
+      </c>
+      <c r="C7" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="16">
+        <v>0.6</v>
+      </c>
+      <c r="E7" s="24"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>60</v>
+      </c>
+      <c r="B8" s="16">
+        <v>600</v>
+      </c>
+      <c r="C8" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="16">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="24"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>75</v>
+      </c>
+      <c r="B9" s="16">
+        <v>980</v>
+      </c>
+      <c r="C9" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="16">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="E9" s="24"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>83</v>
+      </c>
+      <c r="B10" s="16">
+        <v>1515</v>
+      </c>
+      <c r="C10" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="16">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>90</v>
+      </c>
+      <c r="B11" s="16">
+        <v>1800</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0.3</v>
+      </c>
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>100</v>
+      </c>
+      <c r="B12" s="19">
+        <v>2190</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E12" s="25"/>
+    </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E1" location="'Valve List'!A1" display="ValveList"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\BG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\WX\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,14 +24,14 @@
     <sheet name="Valve_30.0_600_3" sheetId="10" r:id="rId10"/>
     <sheet name="Valve_8.0_600_4" sheetId="11" r:id="rId11"/>
     <sheet name="Valve_2.0_1500_3" sheetId="12" r:id="rId12"/>
-    <sheet name="Valve_8.0_V250_5" sheetId="13" r:id="rId13"/>
+    <sheet name="Valve_8.0_2500_5" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="22">
   <si>
     <t>size</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>ValveList</t>
-  </si>
-  <si>
-    <t>V250</t>
   </si>
 </sst>
 </file>
@@ -924,8 +921,8 @@
       <c r="A13" s="2">
         <v>8</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
+      <c r="B13" s="2">
+        <v>2500</v>
       </c>
       <c r="C13" s="2">
         <v>5</v>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\EXT\WX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arge_\Desktop\Projeler\VASTAS-X\Control Valve Sizing(velocity added)\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="8" activeTab="12"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -1574,10 +1574,10 @@
         <v>0</v>
       </c>
       <c r="B2" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" s="16">
-        <v>0</v>
+        <v>0.68</v>
       </c>
       <c r="D2" s="16">
         <v>0.4</v>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -24,7 +24,7 @@
     <sheet name="Valve_30.0_600_3" sheetId="10" r:id="rId10"/>
     <sheet name="Valve_8.0_600_4" sheetId="11" r:id="rId11"/>
     <sheet name="Valve_2.0_1500_3" sheetId="12" r:id="rId12"/>
-    <sheet name="Valve_8.0_2500_5" sheetId="13" r:id="rId13"/>
+    <sheet name="Valve_8.0_1500_3" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
@@ -672,7 +672,9 @@
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="9.140625" style="2"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="20.85546875" style="2" customWidth="1"/>
+    <col min="3" max="5" width="9.140625" style="2"/>
     <col min="6" max="6" width="27.42578125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -922,10 +924,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="2">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="C13" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2">
         <v>1</v>
@@ -1546,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" customWidth="1"/>
@@ -1733,11 +1735,6 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="E12" s="25"/>
-    </row>
-    <row r="22" spans="8:8" x14ac:dyDescent="0.25">
-      <c r="H22">
-        <v>250</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="8" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -24,14 +24,13 @@
     <sheet name="Valve_30.0_600_3" sheetId="10" r:id="rId10"/>
     <sheet name="Valve_8.0_600_4" sheetId="11" r:id="rId11"/>
     <sheet name="Valve_2.0_1500_3" sheetId="12" r:id="rId12"/>
-    <sheet name="Valve_8.0_1500_3" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="22">
   <si>
     <t>size</t>
   </si>
@@ -669,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2"/>
@@ -917,23 +916,6 @@
       </c>
       <c r="F12" s="3" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="2">
-        <v>8</v>
-      </c>
-      <c r="B13" s="2">
-        <v>1500</v>
-      </c>
-      <c r="C13" s="2">
-        <v>3</v>
-      </c>
-      <c r="D13" s="2">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1546,204 +1528,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="5" width="15.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15">
-        <v>0</v>
-      </c>
-      <c r="B2" s="16">
-        <v>5</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="16">
-        <v>0.4</v>
-      </c>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="15">
-        <v>10</v>
-      </c>
-      <c r="B3" s="16">
-        <v>50</v>
-      </c>
-      <c r="C3" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="E3" s="24"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="15">
-        <v>20</v>
-      </c>
-      <c r="B4" s="16">
-        <v>100</v>
-      </c>
-      <c r="C4" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E4" s="24"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="15">
-        <v>30</v>
-      </c>
-      <c r="B5" s="16">
-        <v>150</v>
-      </c>
-      <c r="C5" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="E5" s="24"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="15">
-        <v>40</v>
-      </c>
-      <c r="B6" s="16">
-        <v>250</v>
-      </c>
-      <c r="C6" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="16">
-        <v>0.65</v>
-      </c>
-      <c r="E6" s="24"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="15">
-        <v>50</v>
-      </c>
-      <c r="B7" s="16">
-        <v>400</v>
-      </c>
-      <c r="C7" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="E7" s="24"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="15">
-        <v>60</v>
-      </c>
-      <c r="B8" s="16">
-        <v>600</v>
-      </c>
-      <c r="C8" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="15">
-        <v>75</v>
-      </c>
-      <c r="B9" s="16">
-        <v>980</v>
-      </c>
-      <c r="C9" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="16">
-        <v>0.32800000000000001</v>
-      </c>
-      <c r="E9" s="24"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="15">
-        <v>83</v>
-      </c>
-      <c r="B10" s="16">
-        <v>1515</v>
-      </c>
-      <c r="C10" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E10" s="24"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="15">
-        <v>90</v>
-      </c>
-      <c r="B11" s="16">
-        <v>1800</v>
-      </c>
-      <c r="C11" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
-        <v>100</v>
-      </c>
-      <c r="B12" s="19">
-        <v>2190</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.13700000000000001</v>
-      </c>
-      <c r="E12" s="25"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E1" location="'Valve List'!A1" display="ValveList"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E12"/>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="8" activeTab="11"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -2442,46 +2442,46 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B8" s="16">
-        <v>15.3</v>
+        <v>980</v>
       </c>
       <c r="C8" s="16">
         <v>0.68</v>
       </c>
       <c r="D8" s="16">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
       <c r="E8" s="24"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B9" s="16">
-        <v>15.7</v>
+        <v>1118</v>
       </c>
       <c r="C9" s="16">
         <v>0.68</v>
       </c>
       <c r="D9" s="16">
-        <v>0.80900000000000005</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E9" s="24"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" s="16">
-        <v>16</v>
+        <v>1515</v>
       </c>
       <c r="C10" s="16">
         <v>0.68</v>
       </c>
       <c r="D10" s="16">
-        <v>0.81299999999999994</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="E10" s="24"/>
     </row>
@@ -2490,13 +2490,13 @@
         <v>90</v>
       </c>
       <c r="B11" s="16">
-        <v>16.399999999999999</v>
+        <v>1800</v>
       </c>
       <c r="C11" s="16">
         <v>0.68</v>
       </c>
       <c r="D11" s="16">
-        <v>0.79500000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="24"/>
     </row>
@@ -2505,13 +2505,13 @@
         <v>100</v>
       </c>
       <c r="B12" s="19">
-        <v>16.8</v>
+        <v>2190</v>
       </c>
       <c r="C12" s="19">
         <v>0.68</v>
       </c>
       <c r="D12" s="19">
-        <v>0.76800000000000002</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="E12" s="25"/>
     </row>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" activeTab="5"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -2370,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="16">
-        <v>3.28</v>
+        <v>100</v>
       </c>
       <c r="C3" s="16">
         <v>0.68</v>
@@ -2385,7 +2385,7 @@
         <v>20</v>
       </c>
       <c r="B4" s="16">
-        <v>7.39</v>
+        <v>200</v>
       </c>
       <c r="C4" s="16">
         <v>0.68</v>
@@ -2400,7 +2400,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="16">
-        <v>12</v>
+        <v>300</v>
       </c>
       <c r="C5" s="16">
         <v>0.68</v>
@@ -2415,7 +2415,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="16">
-        <v>14.2</v>
+        <v>400</v>
       </c>
       <c r="C6" s="16">
         <v>0.68</v>
@@ -2430,13 +2430,13 @@
         <v>50</v>
       </c>
       <c r="B7" s="16">
-        <v>14.9</v>
+        <v>600</v>
       </c>
       <c r="C7" s="16">
         <v>0.68</v>
       </c>
       <c r="D7" s="16">
-        <v>0.76400000000000001</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E7" s="24"/>
     </row>
@@ -2451,7 +2451,7 @@
         <v>0.68</v>
       </c>
       <c r="D8" s="16">
-        <v>0.4</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E8" s="24"/>
     </row>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -2361,7 +2361,7 @@
       </c>
       <c r="D2" s="16">
         <f>D3</f>
-        <v>0.58099999999999996</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2376,7 +2376,7 @@
         <v>0.68</v>
       </c>
       <c r="D3" s="16">
-        <v>0.58099999999999996</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E3" s="24"/>
     </row>
@@ -2391,7 +2391,7 @@
         <v>0.68</v>
       </c>
       <c r="D4" s="16">
-        <v>0.60499999999999998</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E4" s="24"/>
     </row>
@@ -2406,7 +2406,7 @@
         <v>0.68</v>
       </c>
       <c r="D5" s="16">
-        <v>0.61699999999999999</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E5" s="24"/>
     </row>
@@ -2421,7 +2421,7 @@
         <v>0.68</v>
       </c>
       <c r="D6" s="16">
-        <v>0.64400000000000002</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E6" s="24"/>
     </row>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -2326,7 +2326,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" style="2" customWidth="1"/>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="B8" s="16">
-        <v>980</v>
+        <v>800</v>
       </c>
       <c r="C8" s="16">
         <v>0.68</v>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B9" s="16">
-        <v>1118</v>
+        <v>850</v>
       </c>
       <c r="C9" s="16">
         <v>0.68</v>
@@ -2472,48 +2472,78 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B10" s="16">
-        <v>1515</v>
+        <v>980</v>
       </c>
       <c r="C10" s="16">
         <v>0.68</v>
       </c>
       <c r="D10" s="16">
-        <v>0.52500000000000002</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E10" s="24"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
+        <v>78</v>
+      </c>
+      <c r="B11" s="16">
+        <v>1118</v>
+      </c>
+      <c r="C11" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="16">
+        <v>0.32800000000000001</v>
+      </c>
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>83</v>
+      </c>
+      <c r="B12" s="16">
+        <v>1515</v>
+      </c>
+      <c r="C12" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="16">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="E12" s="24"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
         <v>90</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B13" s="16">
         <v>1800</v>
       </c>
-      <c r="C11" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="16">
+      <c r="C13" s="16">
+        <v>0.68</v>
+      </c>
+      <c r="D13" s="16">
         <v>0.3</v>
       </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="E13" s="24"/>
+    </row>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
         <v>100</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B14" s="19">
         <v>2190</v>
       </c>
-      <c r="C12" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="C14" s="19">
+        <v>0.68</v>
+      </c>
+      <c r="D14" s="19">
         <v>0.13700000000000001</v>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E14" s="25"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -2326,7 +2326,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" style="2" customWidth="1"/>
@@ -2460,7 +2460,7 @@
         <v>70</v>
       </c>
       <c r="B9" s="16">
-        <v>850</v>
+        <v>1118</v>
       </c>
       <c r="C9" s="16">
         <v>0.68</v>
@@ -2472,78 +2472,48 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B10" s="16">
-        <v>980</v>
+        <v>1515</v>
       </c>
       <c r="C10" s="16">
         <v>0.68</v>
       </c>
       <c r="D10" s="16">
-        <v>0.32800000000000001</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="E10" s="24"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B11" s="16">
-        <v>1118</v>
+        <v>1800</v>
       </c>
       <c r="C11" s="16">
         <v>0.68</v>
       </c>
       <c r="D11" s="16">
-        <v>0.32800000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="24"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="15">
-        <v>83</v>
-      </c>
-      <c r="B12" s="16">
-        <v>1515</v>
-      </c>
-      <c r="C12" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="16">
-        <v>0.52500000000000002</v>
-      </c>
-      <c r="E12" s="24"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="15">
-        <v>90</v>
-      </c>
-      <c r="B13" s="16">
-        <v>1800</v>
-      </c>
-      <c r="C13" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D13" s="16">
-        <v>0.3</v>
-      </c>
-      <c r="E13" s="24"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
         <v>100</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B12" s="19">
         <v>2190</v>
       </c>
-      <c r="C14" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="D14" s="19">
+      <c r="C12" s="19">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="19">
         <v>0.13700000000000001</v>
       </c>
-      <c r="E14" s="25"/>
+      <c r="E12" s="25"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="8" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -356,14 +356,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1161,14 +1161,14 @@
       <c r="A2" s="30">
         <v>0</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2" s="28">
         <v>0</v>
       </c>
       <c r="C2" s="28">
         <v>0</v>
       </c>
       <c r="D2" s="28">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E2" s="26"/>
     </row>
@@ -1176,14 +1176,14 @@
       <c r="A3" s="30">
         <v>10</v>
       </c>
-      <c r="B3" s="31">
+      <c r="B3" s="28">
         <v>0</v>
       </c>
       <c r="C3" s="28">
         <v>0</v>
       </c>
       <c r="D3" s="28">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E3" s="26"/>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="A4" s="30">
         <v>25</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="28">
         <v>18.986232644492688</v>
       </c>
       <c r="C4" s="28">
@@ -1206,7 +1206,7 @@
       <c r="A5" s="30">
         <v>30</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="28">
         <v>44.383454121572619</v>
       </c>
       <c r="C5" s="28">
@@ -1221,7 +1221,7 @@
       <c r="A6" s="30">
         <v>40</v>
       </c>
-      <c r="B6" s="31">
+      <c r="B6" s="28">
         <v>142.05858314674643</v>
       </c>
       <c r="C6" s="28">
@@ -1236,7 +1236,7 @@
       <c r="A7" s="30">
         <v>50</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="28">
         <v>260.93930660910786</v>
       </c>
       <c r="C7" s="28">
@@ -1251,7 +1251,7 @@
       <c r="A8" s="30">
         <v>60</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="28">
         <v>457.75779764190349</v>
       </c>
       <c r="C8" s="28">
@@ -1266,7 +1266,7 @@
       <c r="A9" s="30">
         <v>70</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="28">
         <v>777.14975431228527</v>
       </c>
       <c r="C9" s="28">
@@ -1281,7 +1281,7 @@
       <c r="A10" s="30">
         <v>80</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="28">
         <v>984.39348661726467</v>
       </c>
       <c r="C10" s="28">
@@ -1296,7 +1296,7 @@
       <c r="A11" s="30">
         <v>90</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="28">
         <v>1115.0442453350299</v>
       </c>
       <c r="C11" s="28">
@@ -1308,10 +1308,10 @@
       <c r="E11" s="26"/>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="32">
+      <c r="A12" s="31">
         <v>100</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="29">
         <v>1145.7583178945802</v>
       </c>
       <c r="C12" s="29">
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="16">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="17"/>
     </row>
@@ -1573,14 +1573,14 @@
       <c r="A3" s="15">
         <v>10</v>
       </c>
-      <c r="B3" s="16">
-        <v>5</v>
-      </c>
-      <c r="C3" s="16">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.3</v>
+      <c r="B3" s="32">
+        <v>13.31202233912504</v>
+      </c>
+      <c r="C3" s="32">
+        <v>0.28622500000000001</v>
+      </c>
+      <c r="D3" s="32">
+        <v>0.53500000000000003</v>
       </c>
       <c r="E3" s="17"/>
     </row>
@@ -1588,14 +1588,14 @@
       <c r="A4" s="15">
         <v>20</v>
       </c>
-      <c r="B4" s="16">
-        <v>15</v>
-      </c>
-      <c r="C4" s="16">
-        <v>0.6</v>
-      </c>
-      <c r="D4" s="16">
-        <v>0.4</v>
+      <c r="B4" s="32">
+        <v>32.692258744082537</v>
+      </c>
+      <c r="C4" s="32">
+        <v>0.42902500000000005</v>
+      </c>
+      <c r="D4" s="32">
+        <v>0.65500000000000003</v>
       </c>
       <c r="E4" s="17"/>
     </row>
@@ -1603,14 +1603,14 @@
       <c r="A5" s="15">
         <v>30</v>
       </c>
-      <c r="B5" s="16">
-        <v>30</v>
-      </c>
-      <c r="C5" s="16">
-        <v>0.65</v>
-      </c>
-      <c r="D5" s="16">
-        <v>0.5</v>
+      <c r="B5" s="32">
+        <v>35.413745781315342</v>
+      </c>
+      <c r="C5" s="32">
+        <v>0.38440000000000002</v>
+      </c>
+      <c r="D5" s="32">
+        <v>0.62</v>
       </c>
       <c r="E5" s="17"/>
     </row>
@@ -1618,14 +1618,14 @@
       <c r="A6" s="15">
         <v>40</v>
       </c>
-      <c r="B6" s="16">
-        <v>45</v>
-      </c>
-      <c r="C6" s="16">
-        <v>0.7</v>
-      </c>
-      <c r="D6" s="16">
-        <v>0.6</v>
+      <c r="B6" s="32">
+        <v>38.501103306692336</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0.38440000000000002</v>
+      </c>
+      <c r="D6" s="32">
+        <v>0.62</v>
       </c>
       <c r="E6" s="17"/>
     </row>
@@ -1633,14 +1633,14 @@
       <c r="A7" s="15">
         <v>50</v>
       </c>
-      <c r="B7" s="16">
-        <v>60</v>
-      </c>
-      <c r="C7" s="16">
+      <c r="B7" s="32">
+        <v>42.26830779705768</v>
+      </c>
+      <c r="C7" s="32">
+        <v>0.5625</v>
+      </c>
+      <c r="D7" s="32">
         <v>0.75</v>
-      </c>
-      <c r="D7" s="16">
-        <v>0.65</v>
       </c>
       <c r="E7" s="17"/>
     </row>
@@ -1648,14 +1648,14 @@
       <c r="A8" s="15">
         <v>60</v>
       </c>
-      <c r="B8" s="16">
-        <v>75</v>
-      </c>
-      <c r="C8" s="16">
-        <v>0.8</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0.7</v>
+      <c r="B8" s="32">
+        <v>43.230829971221965</v>
+      </c>
+      <c r="C8" s="32">
+        <v>0.5625</v>
+      </c>
+      <c r="D8" s="32">
+        <v>0.75</v>
       </c>
       <c r="E8" s="17"/>
     </row>
@@ -1663,14 +1663,14 @@
       <c r="A9" s="15">
         <v>70</v>
       </c>
-      <c r="B9" s="16">
-        <v>85</v>
-      </c>
-      <c r="C9" s="16">
-        <v>0.82</v>
-      </c>
-      <c r="D9" s="16">
-        <v>0.75</v>
+      <c r="B9" s="32">
+        <v>44.654446769820602</v>
+      </c>
+      <c r="C9" s="32">
+        <v>0.51122499999999993</v>
+      </c>
+      <c r="D9" s="32">
+        <v>0.71499999999999997</v>
       </c>
       <c r="E9" s="17"/>
     </row>
@@ -1678,14 +1678,14 @@
       <c r="A10" s="15">
         <v>80</v>
       </c>
-      <c r="B10" s="16">
-        <v>92</v>
-      </c>
-      <c r="C10" s="16">
-        <v>0.83</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0.78</v>
+      <c r="B10" s="32">
+        <v>44.719984309519162</v>
+      </c>
+      <c r="C10" s="32">
+        <v>0.51839999999999997</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0.72</v>
       </c>
       <c r="E10" s="17"/>
     </row>
@@ -1693,14 +1693,14 @@
       <c r="A11" s="15">
         <v>90</v>
       </c>
-      <c r="B11" s="16">
-        <v>98</v>
-      </c>
-      <c r="C11" s="16">
-        <v>0.84</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.8</v>
+      <c r="B11" s="32">
+        <v>46.670236841657392</v>
+      </c>
+      <c r="C11" s="32">
+        <v>0.40195600000000004</v>
+      </c>
+      <c r="D11" s="32">
+        <v>0.63400000000000001</v>
       </c>
       <c r="E11" s="17"/>
     </row>
@@ -1708,14 +1708,14 @@
       <c r="A12" s="18">
         <v>100</v>
       </c>
-      <c r="B12" s="19">
-        <v>100</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.85</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.81</v>
+      <c r="B12" s="33">
+        <v>48.040070456780072</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0.403225</v>
+      </c>
+      <c r="D12" s="33">
+        <v>0.63500000000000001</v>
       </c>
       <c r="E12" s="20"/>
     </row>
@@ -1724,6 +1724,7 @@
     <hyperlink ref="E1" location="'Valve List'!A1" display="ValveList"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2154,15 +2155,14 @@
       <c r="A2" s="15">
         <v>0</v>
       </c>
-      <c r="B2" s="16">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0</v>
-      </c>
-      <c r="D2" s="16">
-        <f>D3</f>
-        <v>0.49</v>
+      <c r="B2" s="32">
+        <v>0</v>
+      </c>
+      <c r="C2" s="32">
+        <v>0</v>
+      </c>
+      <c r="D2" s="32">
+        <v>0</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2170,14 +2170,14 @@
       <c r="A3" s="15">
         <v>10</v>
       </c>
-      <c r="B3" s="16">
-        <v>226</v>
-      </c>
-      <c r="C3" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.49</v>
+      <c r="B3" s="32">
+        <v>38.043017182577891</v>
+      </c>
+      <c r="C3" s="32">
+        <v>0.30913600000000008</v>
+      </c>
+      <c r="D3" s="32">
+        <v>0.55600000000000005</v>
       </c>
       <c r="E3" s="24"/>
     </row>
@@ -2185,14 +2185,14 @@
       <c r="A4" s="15">
         <v>20</v>
       </c>
-      <c r="B4" s="16">
-        <v>337</v>
-      </c>
-      <c r="C4" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="16">
-        <v>0.47</v>
+      <c r="B4" s="32">
+        <v>80.246766739175129</v>
+      </c>
+      <c r="C4" s="32">
+        <v>0.35402499999999998</v>
+      </c>
+      <c r="D4" s="32">
+        <v>0.59499999999999997</v>
       </c>
       <c r="E4" s="24"/>
     </row>
@@ -2200,14 +2200,14 @@
       <c r="A5" s="15">
         <v>30</v>
       </c>
-      <c r="B5" s="16">
-        <v>436</v>
-      </c>
-      <c r="C5" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="16">
-        <v>0.42699999999999999</v>
+      <c r="B5" s="32">
+        <v>118.19476772685371</v>
+      </c>
+      <c r="C5" s="32">
+        <v>0.37209999999999999</v>
+      </c>
+      <c r="D5" s="32">
+        <v>0.61</v>
       </c>
       <c r="E5" s="24"/>
     </row>
@@ -2215,14 +2215,14 @@
       <c r="A6" s="15">
         <v>40</v>
       </c>
-      <c r="B6" s="16">
-        <v>502</v>
-      </c>
-      <c r="C6" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="16">
-        <v>0.45200000000000001</v>
+      <c r="B6" s="32">
+        <v>139.21847882617462</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0.48999999999999994</v>
+      </c>
+      <c r="D6" s="32">
+        <v>0.7</v>
       </c>
       <c r="E6" s="24"/>
     </row>
@@ -2230,14 +2230,14 @@
       <c r="A7" s="15">
         <v>50</v>
       </c>
-      <c r="B7" s="16">
-        <v>581</v>
-      </c>
-      <c r="C7" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="16">
-        <v>0.46800000000000003</v>
+      <c r="B7" s="32">
+        <v>155.26096587806657</v>
+      </c>
+      <c r="C7" s="32">
+        <v>0.53289999999999993</v>
+      </c>
+      <c r="D7" s="32">
+        <v>0.73</v>
       </c>
       <c r="E7" s="24"/>
     </row>
@@ -2245,14 +2245,14 @@
       <c r="A8" s="15">
         <v>60</v>
       </c>
-      <c r="B8" s="16">
-        <v>641</v>
-      </c>
-      <c r="C8" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0.51200000000000001</v>
+      <c r="B8" s="32">
+        <v>156.95350477559671</v>
+      </c>
+      <c r="C8" s="32">
+        <v>0.5776</v>
+      </c>
+      <c r="D8" s="32">
+        <v>0.76</v>
       </c>
       <c r="E8" s="24"/>
     </row>
@@ -2260,14 +2260,14 @@
       <c r="A9" s="15">
         <v>70</v>
       </c>
-      <c r="B9" s="16">
-        <v>655</v>
-      </c>
-      <c r="C9" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="16">
-        <v>0.624</v>
+      <c r="B9" s="32">
+        <v>169.70553538262996</v>
+      </c>
+      <c r="C9" s="32">
+        <v>0.53289999999999993</v>
+      </c>
+      <c r="D9" s="32">
+        <v>0.73</v>
       </c>
       <c r="E9" s="24"/>
     </row>
@@ -2275,14 +2275,14 @@
       <c r="A10" s="15">
         <v>80</v>
       </c>
-      <c r="B10" s="16">
-        <v>659</v>
-      </c>
-      <c r="C10" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0.70299999999999996</v>
+      <c r="B10" s="32">
+        <v>171.43697025221709</v>
+      </c>
+      <c r="C10" s="32">
+        <v>0.47609999999999991</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0.69</v>
       </c>
       <c r="E10" s="24"/>
     </row>
@@ -2290,14 +2290,14 @@
       <c r="A11" s="15">
         <v>90</v>
       </c>
-      <c r="B11" s="16">
-        <v>659</v>
-      </c>
-      <c r="C11" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.70299999999999996</v>
+      <c r="B11" s="32">
+        <v>176.87229528170275</v>
+      </c>
+      <c r="C11" s="32">
+        <v>0.48163599999999995</v>
+      </c>
+      <c r="D11" s="32">
+        <v>0.69399999999999995</v>
       </c>
       <c r="E11" s="24"/>
     </row>
@@ -2305,14 +2305,14 @@
       <c r="A12" s="18">
         <v>100</v>
       </c>
-      <c r="B12" s="19">
-        <v>681</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.70099999999999996</v>
+      <c r="B12" s="33">
+        <v>182.5517650824853</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0.48999999999999994</v>
+      </c>
+      <c r="D12" s="33">
+        <v>0.7</v>
       </c>
       <c r="E12" s="25"/>
     </row>
@@ -2353,13 +2353,13 @@
       <c r="A2" s="15">
         <v>0</v>
       </c>
-      <c r="B2" s="16">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0</v>
-      </c>
-      <c r="D2" s="16">
+      <c r="B2" s="32">
+        <v>0</v>
+      </c>
+      <c r="C2" s="32">
+        <v>0</v>
+      </c>
+      <c r="D2" s="32">
         <f>D3</f>
         <v>0.32800000000000001</v>
       </c>
@@ -2369,13 +2369,13 @@
       <c r="A3" s="15">
         <v>10</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="32">
         <v>100</v>
       </c>
-      <c r="C3" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="16">
+      <c r="C3" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D3" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E3" s="24"/>
@@ -2384,13 +2384,13 @@
       <c r="A4" s="15">
         <v>20</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="32">
         <v>200</v>
       </c>
-      <c r="C4" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="16">
+      <c r="C4" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D4" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E4" s="24"/>
@@ -2399,13 +2399,13 @@
       <c r="A5" s="15">
         <v>30</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="32">
         <v>300</v>
       </c>
-      <c r="C5" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D5" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E5" s="24"/>
@@ -2414,13 +2414,13 @@
       <c r="A6" s="15">
         <v>40</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="32">
         <v>400</v>
       </c>
-      <c r="C6" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="16">
+      <c r="C6" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D6" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E6" s="24"/>
@@ -2429,13 +2429,13 @@
       <c r="A7" s="15">
         <v>50</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="32">
         <v>600</v>
       </c>
-      <c r="C7" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="16">
+      <c r="C7" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D7" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E7" s="24"/>
@@ -2444,13 +2444,13 @@
       <c r="A8" s="15">
         <v>60</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="32">
         <v>800</v>
       </c>
-      <c r="C8" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="C8" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D8" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E8" s="24"/>
@@ -2459,13 +2459,13 @@
       <c r="A9" s="15">
         <v>70</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="32">
         <v>1118</v>
       </c>
-      <c r="C9" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="16">
+      <c r="C9" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D9" s="32">
         <v>0.32800000000000001</v>
       </c>
       <c r="E9" s="24"/>
@@ -2474,13 +2474,13 @@
       <c r="A10" s="15">
         <v>80</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="32">
         <v>1515</v>
       </c>
-      <c r="C10" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="16">
+      <c r="C10" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D10" s="32">
         <v>0.52500000000000002</v>
       </c>
       <c r="E10" s="24"/>
@@ -2489,13 +2489,13 @@
       <c r="A11" s="15">
         <v>90</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="32">
         <v>1800</v>
       </c>
-      <c r="C11" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="16">
+      <c r="C11" s="32">
+        <v>0.68</v>
+      </c>
+      <c r="D11" s="32">
         <v>0.3</v>
       </c>
       <c r="E11" s="24"/>
@@ -2504,13 +2504,13 @@
       <c r="A12" s="18">
         <v>100</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="33">
         <v>2190</v>
       </c>
-      <c r="C12" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="C12" s="33">
+        <v>0.68</v>
+      </c>
+      <c r="D12" s="33">
         <v>0.13700000000000001</v>
       </c>
       <c r="E12" s="25"/>
@@ -2552,15 +2552,14 @@
       <c r="A2" s="15">
         <v>0</v>
       </c>
-      <c r="B2" s="16">
-        <v>0</v>
-      </c>
-      <c r="C2" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D2" s="16">
-        <f>D3</f>
-        <v>0.58099999999999996</v>
+      <c r="B2" s="32">
+        <v>0</v>
+      </c>
+      <c r="C2" s="32">
+        <v>0</v>
+      </c>
+      <c r="D2" s="32">
+        <v>0</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2568,14 +2567,14 @@
       <c r="A3" s="15">
         <v>10</v>
       </c>
-      <c r="B3" s="16">
-        <v>3.28</v>
-      </c>
-      <c r="C3" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D3" s="16">
-        <v>0.58099999999999996</v>
+      <c r="B3" s="32">
+        <v>50</v>
+      </c>
+      <c r="C3" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D3" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E3" s="24"/>
     </row>
@@ -2583,14 +2582,14 @@
       <c r="A4" s="15">
         <v>20</v>
       </c>
-      <c r="B4" s="16">
-        <v>7.39</v>
-      </c>
-      <c r="C4" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D4" s="16">
-        <v>0.60499999999999998</v>
+      <c r="B4" s="32">
+        <v>100</v>
+      </c>
+      <c r="C4" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D4" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E4" s="24"/>
     </row>
@@ -2598,14 +2597,14 @@
       <c r="A5" s="15">
         <v>30</v>
       </c>
-      <c r="B5" s="16">
-        <v>12</v>
-      </c>
-      <c r="C5" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D5" s="16">
-        <v>0.61699999999999999</v>
+      <c r="B5" s="32">
+        <v>200</v>
+      </c>
+      <c r="C5" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D5" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E5" s="24"/>
     </row>
@@ -2613,14 +2612,14 @@
       <c r="A6" s="15">
         <v>40</v>
       </c>
-      <c r="B6" s="16">
-        <v>14.2</v>
-      </c>
-      <c r="C6" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D6" s="16">
-        <v>0.64400000000000002</v>
+      <c r="B6" s="32">
+        <v>300</v>
+      </c>
+      <c r="C6" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D6" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E6" s="24"/>
     </row>
@@ -2628,14 +2627,14 @@
       <c r="A7" s="15">
         <v>50</v>
       </c>
-      <c r="B7" s="16">
-        <v>14.9</v>
-      </c>
-      <c r="C7" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D7" s="16">
-        <v>0.76400000000000001</v>
+      <c r="B7" s="32">
+        <v>500</v>
+      </c>
+      <c r="C7" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D7" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E7" s="24"/>
     </row>
@@ -2643,14 +2642,14 @@
       <c r="A8" s="15">
         <v>60</v>
       </c>
-      <c r="B8" s="16">
-        <v>15.3</v>
-      </c>
-      <c r="C8" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D8" s="16">
-        <v>0.79</v>
+      <c r="B8" s="32">
+        <v>700</v>
+      </c>
+      <c r="C8" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D8" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E8" s="24"/>
     </row>
@@ -2658,14 +2657,14 @@
       <c r="A9" s="15">
         <v>70</v>
       </c>
-      <c r="B9" s="16">
-        <v>15.7</v>
-      </c>
-      <c r="C9" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D9" s="16">
-        <v>0.80900000000000005</v>
+      <c r="B9" s="32">
+        <v>900</v>
+      </c>
+      <c r="C9" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D9" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E9" s="24"/>
     </row>
@@ -2673,14 +2672,14 @@
       <c r="A10" s="15">
         <v>80</v>
       </c>
-      <c r="B10" s="16">
-        <v>16</v>
-      </c>
-      <c r="C10" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D10" s="16">
-        <v>0.81299999999999994</v>
+      <c r="B10" s="32">
+        <v>1100</v>
+      </c>
+      <c r="C10" s="32">
+        <v>0.61622500000000002</v>
+      </c>
+      <c r="D10" s="32">
+        <v>0.78500000000000003</v>
       </c>
       <c r="E10" s="24"/>
     </row>
@@ -2688,14 +2687,14 @@
       <c r="A11" s="15">
         <v>90</v>
       </c>
-      <c r="B11" s="16">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="C11" s="16">
-        <v>0.68</v>
-      </c>
-      <c r="D11" s="16">
-        <v>0.79500000000000004</v>
+      <c r="B11" s="32">
+        <v>1323.0184453148931</v>
+      </c>
+      <c r="C11" s="32">
+        <v>0.47609999999999991</v>
+      </c>
+      <c r="D11" s="32">
+        <v>0.69</v>
       </c>
       <c r="E11" s="24"/>
     </row>
@@ -2703,14 +2702,14 @@
       <c r="A12" s="18">
         <v>100</v>
       </c>
-      <c r="B12" s="19">
-        <v>16.8</v>
-      </c>
-      <c r="C12" s="19">
-        <v>0.68</v>
-      </c>
-      <c r="D12" s="19">
-        <v>0.76800000000000002</v>
+      <c r="B12" s="33">
+        <v>1338.5243484781358</v>
+      </c>
+      <c r="C12" s="33">
+        <v>0.37209999999999999</v>
+      </c>
+      <c r="D12" s="33">
+        <v>0.61</v>
       </c>
       <c r="E12" s="25"/>
     </row>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="8" activeTab="10"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B8" s="32">
-        <v>800</v>
+        <v>980</v>
       </c>
       <c r="C8" s="32">
         <v>0.68</v>
@@ -2457,7 +2457,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B9" s="32">
         <v>1118</v>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" s="32">
         <v>1515</v>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="5"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -2162,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="D2" s="32">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="E2" s="24"/>
     </row>
@@ -2177,7 +2177,7 @@
         <v>0.30913600000000008</v>
       </c>
       <c r="D3" s="32">
-        <v>0.55600000000000005</v>
+        <v>0.95</v>
       </c>
       <c r="E3" s="24"/>
     </row>
@@ -2192,7 +2192,7 @@
         <v>0.35402499999999998</v>
       </c>
       <c r="D4" s="32">
-        <v>0.59499999999999997</v>
+        <v>0.95</v>
       </c>
       <c r="E4" s="24"/>
     </row>
@@ -2207,7 +2207,7 @@
         <v>0.37209999999999999</v>
       </c>
       <c r="D5" s="32">
-        <v>0.61</v>
+        <v>0.95</v>
       </c>
       <c r="E5" s="24"/>
     </row>
@@ -2222,7 +2222,7 @@
         <v>0.48999999999999994</v>
       </c>
       <c r="D6" s="32">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="E6" s="24"/>
     </row>
@@ -2237,7 +2237,7 @@
         <v>0.53289999999999993</v>
       </c>
       <c r="D7" s="32">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="E7" s="24"/>
     </row>
@@ -2252,7 +2252,7 @@
         <v>0.5776</v>
       </c>
       <c r="D8" s="32">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="E8" s="24"/>
     </row>
@@ -2267,7 +2267,7 @@
         <v>0.53289999999999993</v>
       </c>
       <c r="D9" s="32">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
       <c r="E9" s="24"/>
     </row>
@@ -2282,7 +2282,7 @@
         <v>0.47609999999999991</v>
       </c>
       <c r="D10" s="32">
-        <v>0.69</v>
+        <v>0.95</v>
       </c>
       <c r="E10" s="24"/>
     </row>
@@ -2297,7 +2297,7 @@
         <v>0.48163599999999995</v>
       </c>
       <c r="D11" s="32">
-        <v>0.69399999999999995</v>
+        <v>0.95</v>
       </c>
       <c r="E11" s="24"/>
     </row>
@@ -2312,7 +2312,7 @@
         <v>0.48999999999999994</v>
       </c>
       <c r="D12" s="33">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="E12" s="25"/>
     </row>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="4"/>
+    <workbookView xWindow="3255" yWindow="3255" windowWidth="28800" windowHeight="15465" firstSheet="3" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Valve List" sheetId="1" r:id="rId1"/>
@@ -2326,13 +2326,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>0</v>
       </c>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E2" s="24"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <v>10</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E3" s="24"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>20</v>
       </c>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E4" s="24"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <v>30</v>
       </c>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E5" s="24"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <v>40</v>
       </c>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E6" s="24"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>50</v>
       </c>
@@ -2436,11 +2436,11 @@
         <v>0.68</v>
       </c>
       <c r="D7" s="32">
-        <v>0.32800000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="E7" s="24"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>75</v>
       </c>
@@ -2451,11 +2451,14 @@
         <v>0.68</v>
       </c>
       <c r="D8" s="32">
+        <v>0.31</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="H8" s="32">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>78</v>
       </c>
@@ -2466,11 +2469,14 @@
         <v>0.68</v>
       </c>
       <c r="D9" s="32">
+        <v>0.31</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="H9" s="32">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E9" s="24"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>83</v>
       </c>
@@ -2481,11 +2487,14 @@
         <v>0.68</v>
       </c>
       <c r="D10" s="32">
+        <v>0.31</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="H10" s="32">
         <v>0.52500000000000002</v>
       </c>
-      <c r="E10" s="24"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>90</v>
       </c>
@@ -2496,11 +2505,14 @@
         <v>0.68</v>
       </c>
       <c r="D11" s="32">
+        <v>0.31</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="H11" s="32">
         <v>0.3</v>
       </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>100</v>
       </c>
@@ -2511,9 +2523,12 @@
         <v>0.68</v>
       </c>
       <c r="D12" s="33">
+        <v>0.31</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="H12" s="33">
         <v>0.13700000000000001</v>
       </c>
-      <c r="E12" s="25"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -2326,13 +2326,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15">
         <v>0</v>
       </c>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="E2" s="24"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="15">
         <v>10</v>
       </c>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="E3" s="24"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="15">
         <v>20</v>
       </c>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="E4" s="24"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="15">
         <v>30</v>
       </c>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="E5" s="24"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="15">
         <v>40</v>
       </c>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="E6" s="24"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="15">
         <v>50</v>
       </c>
@@ -2436,11 +2436,11 @@
         <v>0.68</v>
       </c>
       <c r="D7" s="32">
-        <v>0.31</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E7" s="24"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="15">
         <v>75</v>
       </c>
@@ -2451,14 +2451,11 @@
         <v>0.68</v>
       </c>
       <c r="D8" s="32">
-        <v>0.31</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E8" s="24"/>
-      <c r="H8" s="32">
-        <v>0.32800000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="15">
         <v>78</v>
       </c>
@@ -2469,14 +2466,11 @@
         <v>0.68</v>
       </c>
       <c r="D9" s="32">
-        <v>0.31</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E9" s="24"/>
-      <c r="H9" s="32">
-        <v>0.32800000000000001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="15">
         <v>83</v>
       </c>
@@ -2487,14 +2481,11 @@
         <v>0.68</v>
       </c>
       <c r="D10" s="32">
-        <v>0.31</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="E10" s="24"/>
-      <c r="H10" s="32">
-        <v>0.52500000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="15">
         <v>90</v>
       </c>
@@ -2505,14 +2496,11 @@
         <v>0.68</v>
       </c>
       <c r="D11" s="32">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="E11" s="24"/>
-      <c r="H11" s="32">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>100</v>
       </c>
@@ -2523,12 +2511,9 @@
         <v>0.68</v>
       </c>
       <c r="D12" s="33">
-        <v>0.31</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="E12" s="25"/>
-      <c r="H12" s="33">
-        <v>0.13700000000000001</v>
-      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/valve_database.xlsx
+++ b/valve_database.xlsx
@@ -2326,13 +2326,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="15.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>17</v>
       </c>
@@ -2349,7 +2349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <v>0</v>
       </c>
@@ -2359,13 +2359,12 @@
       <c r="C2" s="32">
         <v>0</v>
       </c>
-      <c r="D2" s="32">
-        <f>D3</f>
-        <v>0.32800000000000001</v>
+      <c r="D2" s="33">
+        <v>0.13700000000000001</v>
       </c>
       <c r="E2" s="24"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15">
         <v>10</v>
       </c>
@@ -2375,12 +2374,12 @@
       <c r="C3" s="32">
         <v>0.68</v>
       </c>
-      <c r="D3" s="32">
-        <v>0.32800000000000001</v>
+      <c r="D3" s="33">
+        <v>0.13700000000000001</v>
       </c>
       <c r="E3" s="24"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>20</v>
       </c>
@@ -2390,12 +2389,12 @@
       <c r="C4" s="32">
         <v>0.68</v>
       </c>
-      <c r="D4" s="32">
-        <v>0.32800000000000001</v>
+      <c r="D4" s="33">
+        <v>0.13700000000000001</v>
       </c>
       <c r="E4" s="24"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>30</v>
       </c>
@@ -2405,12 +2404,12 @@
       <c r="C5" s="32">
         <v>0.68</v>
       </c>
-      <c r="D5" s="32">
-        <v>0.32800000000000001</v>
+      <c r="D5" s="33">
+        <v>0.13700000000000001</v>
       </c>
       <c r="E5" s="24"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>40</v>
       </c>
@@ -2420,12 +2419,12 @@
       <c r="C6" s="32">
         <v>0.68</v>
       </c>
-      <c r="D6" s="32">
-        <v>0.32800000000000001</v>
+      <c r="D6" s="33">
+        <v>0.13700000000000001</v>
       </c>
       <c r="E6" s="24"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <v>50</v>
       </c>
@@ -2435,12 +2434,15 @@
       <c r="C7" s="32">
         <v>0.68</v>
       </c>
-      <c r="D7" s="32">
+      <c r="D7" s="33">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E7" s="24"/>
+      <c r="H7" s="32">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E7" s="24"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>75</v>
       </c>
@@ -2450,12 +2452,15 @@
       <c r="C8" s="32">
         <v>0.68</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="H8" s="32">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E8" s="24"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
         <v>78</v>
       </c>
@@ -2465,12 +2470,15 @@
       <c r="C9" s="32">
         <v>0.68</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="H9" s="32">
         <v>0.32800000000000001</v>
       </c>
-      <c r="E9" s="24"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
         <v>83</v>
       </c>
@@ -2480,12 +2488,15 @@
       <c r="C10" s="32">
         <v>0.68</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E10" s="24"/>
+      <c r="H10" s="32">
         <v>0.52500000000000002</v>
       </c>
-      <c r="E10" s="24"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15">
         <v>90</v>
       </c>
@@ -2495,12 +2506,15 @@
       <c r="C11" s="32">
         <v>0.68</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
+        <v>0.13700000000000001</v>
+      </c>
+      <c r="E11" s="24"/>
+      <c r="H11" s="32">
         <v>0.3</v>
       </c>
-      <c r="E11" s="24"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18">
         <v>100</v>
       </c>
@@ -2514,6 +2528,9 @@
         <v>0.13700000000000001</v>
       </c>
       <c r="E12" s="25"/>
+      <c r="H12" s="33">
+        <v>0.13700000000000001</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
